--- a/ResourcesTH/distributorProfileBulkUpdate.xlsx
+++ b/ResourcesTH/distributorProfileBulkUpdate.xlsx
@@ -123,10 +123,10 @@
     <t>N</t>
   </si>
   <si>
-    <t>Sun</t>
-  </si>
-  <si>
     <t>03001</t>
+  </si>
+  <si>
+    <t>SUN</t>
   </si>
 </sst>
 </file>
@@ -550,7 +550,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
         <v>27</v>
@@ -577,7 +577,7 @@
         <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
         <v>29</v>
